--- a/docs/workbook-split/dateien/Regionen.xlsx
+++ b/docs/workbook-split/dateien/Regionen.xlsx
@@ -667,37 +667,29 @@
           <t>West</t>
         </is>
       </c>
-      <c r="D7" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$213:$D$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C7)</f>
-        <v/>
-      </c>
-      <c r="E7" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$213:$E$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$H$213:$H$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C7)</f>
-        <v/>
-      </c>
-      <c r="G7" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$I$213:$I$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C7)</f>
-        <v/>
-      </c>
-      <c r="H7" s="7">
-        <f>IF(F7=0,"n.a.",G7/F7)</f>
-        <v/>
-      </c>
-      <c r="I7" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$R$22:$R$68,'[D KLR.xlsx]D KLR'!$A$22:$A$68,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$22:$B$68,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$D$22:$D$68,C7)</f>
-        <v/>
-      </c>
-      <c r="J7" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$T$22:$T$68,'[D KLR.xlsx]D KLR'!$A$22:$A$68,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$22:$B$68,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$D$22:$D$68,C7)</f>
-        <v/>
-      </c>
-      <c r="K7" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$U$22:$U$68,'[D KLR.xlsx]D KLR'!$A$22:$A$68,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$22:$B$68,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$D$22:$D$68,C7)</f>
-        <v/>
+      <c r="D7" s="6" t="n">
+        <v>4131202.42</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>4674021.93</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>8805224.35</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>269409.4700000001</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>0.03059654805956195</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>846982.03</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>764372.9399999999</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>1190671.26</v>
       </c>
       <c r="L7" s="1" t="n"/>
       <c r="M7" s="1" t="n"/>
@@ -712,37 +704,29 @@
           <t>Süd-West</t>
         </is>
       </c>
-      <c r="D8" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$213:$D$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C8)</f>
-        <v/>
-      </c>
-      <c r="E8" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$213:$E$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$H$213:$H$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C8)</f>
-        <v/>
-      </c>
-      <c r="G8" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$I$213:$I$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="7">
-        <f>IF(F8=0,"n.a.",G8/F8)</f>
-        <v/>
-      </c>
-      <c r="I8" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$R$22:$R$68,'[D KLR.xlsx]D KLR'!$A$22:$A$68,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$22:$B$68,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$D$22:$D$68,C8)</f>
-        <v/>
-      </c>
-      <c r="J8" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$T$22:$T$68,'[D KLR.xlsx]D KLR'!$A$22:$A$68,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$22:$B$68,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$D$22:$D$68,C8)</f>
-        <v/>
-      </c>
-      <c r="K8" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$U$22:$U$68,'[D KLR.xlsx]D KLR'!$A$22:$A$68,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$22:$B$68,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$D$22:$D$68,C8)</f>
-        <v/>
+      <c r="D8" s="6" t="n">
+        <v>2848882.72</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-244125.67</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>2604757.05</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-643673</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>-0.2471144093841688</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>205676.31</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>146076.92</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>350316.48</v>
       </c>
       <c r="L8" s="1" t="n"/>
       <c r="M8" s="1" t="n"/>
@@ -757,37 +741,29 @@
           <t>Ost</t>
         </is>
       </c>
-      <c r="D9" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$213:$D$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C9)</f>
-        <v/>
-      </c>
-      <c r="E9" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$213:$E$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$H$213:$H$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C9)</f>
-        <v/>
-      </c>
-      <c r="G9" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$I$213:$I$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="7">
-        <f>IF(F9=0,"n.a.",G9/F9)</f>
-        <v/>
-      </c>
-      <c r="I9" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$R$22:$R$68,'[D KLR.xlsx]D KLR'!$A$22:$A$68,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$22:$B$68,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$D$22:$D$68,C9)</f>
-        <v/>
-      </c>
-      <c r="J9" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$T$22:$T$68,'[D KLR.xlsx]D KLR'!$A$22:$A$68,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$22:$B$68,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$D$22:$D$68,C9)</f>
-        <v/>
-      </c>
-      <c r="K9" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$U$22:$U$68,'[D KLR.xlsx]D KLR'!$A$22:$A$68,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$22:$B$68,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$D$22:$D$68,C9)</f>
-        <v/>
+      <c r="D9" s="6" t="n">
+        <v>4868208.13</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-58571.6100000001</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>4809636.52</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>600052.3799999999</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>0.1247604423961751</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1524187.84</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1470725.2</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>1736138.8</v>
       </c>
       <c r="L9" s="1" t="n"/>
       <c r="M9" s="1" t="n"/>
@@ -802,37 +778,29 @@
           <t>Berlin</t>
         </is>
       </c>
-      <c r="D10" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$213:$D$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C10)</f>
-        <v/>
-      </c>
-      <c r="E10" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$213:$E$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$H$213:$H$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C10)</f>
-        <v/>
-      </c>
-      <c r="G10" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$I$213:$I$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="7">
-        <f>IF(F10=0,"n.a.",G10/F10)</f>
-        <v/>
-      </c>
-      <c r="I10" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$R$22:$R$68,'[D KLR.xlsx]D KLR'!$A$22:$A$68,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$22:$B$68,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$D$22:$D$68,C10)</f>
-        <v/>
-      </c>
-      <c r="J10" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$T$22:$T$68,'[D KLR.xlsx]D KLR'!$A$22:$A$68,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$22:$B$68,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$D$22:$D$68,C10)</f>
-        <v/>
-      </c>
-      <c r="K10" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$U$22:$U$68,'[D KLR.xlsx]D KLR'!$A$22:$A$68,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$22:$B$68,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$D$22:$D$68,C10)</f>
-        <v/>
+      <c r="D10" s="6" t="n">
+        <v>403567.64</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>537519.8100000001</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>941087.45</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-7759.919999999998</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>-0.00824569491389987</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>271457.81</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>255345.82</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>229235.59</v>
       </c>
       <c r="L10" s="1" t="n"/>
       <c r="M10" s="1" t="n"/>
@@ -847,37 +815,29 @@
           <t>Verwaltung</t>
         </is>
       </c>
-      <c r="D11" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$213:$D$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$213:$E$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C11)</f>
-        <v/>
-      </c>
-      <c r="F11" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$H$213:$H$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="6">
-        <f>SUMIFS('[D Finanzen.xlsx]D Finanzen'!$I$213:$I$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,C11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="7">
-        <f>IF(F11=0,"n.a.",G11/F11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$R$22:$R$68,'[D KLR.xlsx]D KLR'!$A$22:$A$68,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$22:$B$68,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$D$22:$D$68,C11)</f>
-        <v/>
-      </c>
-      <c r="J11" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$T$22:$T$68,'[D KLR.xlsx]D KLR'!$A$22:$A$68,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$22:$B$68,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$D$22:$D$68,C11)</f>
-        <v/>
-      </c>
-      <c r="K11" s="6">
-        <f>SUMIFS('[D KLR.xlsx]D KLR'!$U$22:$U$68,'[D KLR.xlsx]D KLR'!$A$22:$A$68,'[Steuerung.xlsx]Steuerung'!$F$6,'[D KLR.xlsx]D KLR'!$B$22:$B$68,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7,'[D KLR.xlsx]D KLR'!$D$22:$D$68,C11)</f>
-        <v/>
+      <c r="D11" s="6" t="n">
+        <v>1517.940000000001</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>1517.940000000001</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-1093323.57</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>-720.2679750187752</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>-567173.37</v>
       </c>
       <c r="L11" s="1" t="n"/>
       <c r="M11" s="1" t="n"/>
@@ -909,37 +869,29 @@
           <t>Gesamt</t>
         </is>
       </c>
-      <c r="D13" s="9">
-        <f>SUM(D7:D11)</f>
-        <v/>
-      </c>
-      <c r="E13" s="9">
-        <f>SUM(E7:E11)</f>
-        <v/>
-      </c>
-      <c r="F13" s="9">
-        <f>SUM(F7:F11)</f>
-        <v/>
-      </c>
-      <c r="G13" s="9">
-        <f>SUM(G7:G11)</f>
-        <v/>
-      </c>
-      <c r="H13" s="10">
-        <f>IF(F13=0,"n.a.",G13/F13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="9">
-        <f>SUM(I7:I11)</f>
-        <v/>
-      </c>
-      <c r="J13" s="9">
-        <f>SUM(J7:J11)</f>
-        <v/>
-      </c>
-      <c r="K13" s="9">
-        <f>SUM(K7:K11)</f>
-        <v/>
+      <c r="D13" s="9" t="n">
+        <v>12253378.85</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>4908844.459999999</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>17162223.31</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>-875294.6400000001</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>-0.05100123825390313</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>2848303.99</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>2636520.879999999</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>2939188.76</v>
       </c>
       <c r="L13" s="1" t="n"/>
       <c r="M13" s="1" t="n"/>
@@ -1341,9 +1293,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n"/>
-      <c r="E37" s="1">
-        <f>'[Steuerung.xlsx]Steuerung'!F9</f>
-        <v/>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
       </c>
       <c r="F37" s="1" t="n"/>
       <c r="G37" s="1" t="n"/>
@@ -1420,25 +1373,20 @@
       <c r="C40" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D40" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C40,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$213:$D$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C40,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="E40" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C40,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$213:$E$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C40,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="F40" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C40,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$H$213:$H$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C40,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="G40" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C40,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$I$213:$I$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C40,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="H40" s="7">
-        <f>IF(F40="","",IF(F40=0,"n.a.",G40/F40))</f>
-        <v/>
+      <c r="D40" s="6" t="n">
+        <v>313216.91</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>728945.6</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>1042162.51</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>357470.84</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>0.3430087309511834</v>
       </c>
       <c r="I40" s="1" t="n"/>
       <c r="J40" s="1" t="n"/>
@@ -1454,25 +1402,20 @@
       <c r="C41" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="D41" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C41,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$213:$D$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C41,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="E41" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C41,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$213:$E$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C41,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="F41" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C41,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$H$213:$H$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C41,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="G41" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C41,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$I$213:$I$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C41,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="H41" s="7">
-        <f>IF(F41="","",IF(F41=0,"n.a.",G41/F41))</f>
-        <v/>
+      <c r="D41" s="6" t="n">
+        <v>403993.79</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>799162.23</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>1203156.02</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>182473.85</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>0.1516626663265168</v>
       </c>
       <c r="I41" s="1" t="n"/>
       <c r="J41" s="1" t="n"/>
@@ -1488,25 +1431,20 @@
       <c r="C42" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="D42" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C42,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$213:$D$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C42,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="E42" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C42,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$213:$E$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C42,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="F42" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C42,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$H$213:$H$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C42,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="G42" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C42,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$I$213:$I$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C42,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="H42" s="7">
-        <f>IF(F42="","",IF(F42=0,"n.a.",G42/F42))</f>
-        <v/>
+      <c r="D42" s="6" t="n">
+        <v>255457.91</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>855886.16</v>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>1111344.07</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>197793.93</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>0.1779772217617538</v>
       </c>
       <c r="I42" s="1" t="n"/>
       <c r="J42" s="1" t="n"/>
@@ -1522,25 +1460,20 @@
       <c r="C43" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="D43" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C43,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$213:$D$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C43,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="E43" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C43,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$213:$E$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C43,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="F43" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C43,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$H$213:$H$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C43,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="G43" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C43,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$I$213:$I$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C43,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="H43" s="7">
-        <f>IF(F43="","",IF(F43=0,"n.a.",G43/F43))</f>
-        <v/>
+      <c r="D43" s="6" t="n">
+        <v>146261.59</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>1000014.67</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>1146276.26</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>46994.64</v>
+      </c>
+      <c r="H43" s="7" t="n">
+        <v>0.04099765618455711</v>
       </c>
       <c r="I43" s="1" t="n"/>
       <c r="J43" s="1" t="n"/>
@@ -1556,25 +1489,20 @@
       <c r="C44" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D44" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C44,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$213:$D$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C44,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="E44" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C44,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$213:$E$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C44,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="F44" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C44,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$H$213:$H$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C44,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="G44" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C44,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$I$213:$I$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C44,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="H44" s="7">
-        <f>IF(F44="","",IF(F44=0,"n.a.",G44/F44))</f>
-        <v/>
+      <c r="D44" s="6" t="n">
+        <v>714986.63</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>-300461.68</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>414524.95</v>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>52843.11</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>0.127478719917824</v>
       </c>
       <c r="I44" s="1" t="n"/>
       <c r="J44" s="1" t="n"/>
@@ -1590,25 +1518,20 @@
       <c r="C45" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="D45" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C45,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$213:$D$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C45,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="E45" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C45,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$213:$E$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C45,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="F45" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C45,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$H$213:$H$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C45,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="G45" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C45,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$I$213:$I$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C45,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="H45" s="7">
-        <f>IF(F45="","",IF(F45=0,"n.a.",G45/F45))</f>
-        <v/>
+      <c r="D45" s="6" t="n">
+        <v>998990.23</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>405367.04</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>1404357.27</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>43638.48</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>0.03107363128472287</v>
       </c>
       <c r="I45" s="1" t="n"/>
       <c r="J45" s="1" t="n"/>
@@ -1624,25 +1547,20 @@
       <c r="C46" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="D46" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C46,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$213:$D$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C46,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="E46" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C46,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$213:$E$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C46,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="F46" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C46,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$H$213:$H$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C46,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="G46" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C46,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$I$213:$I$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C46,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="H46" s="7">
-        <f>IF(F46="","",IF(F46=0,"n.a.",G46/F46))</f>
-        <v/>
+      <c r="D46" s="6" t="n">
+        <v>214452.93</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>376025.24</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>590478.17</v>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>-356308.7</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>-0.6034240012632474</v>
       </c>
       <c r="I46" s="1" t="n"/>
       <c r="J46" s="1" t="n"/>
@@ -1658,25 +1576,20 @@
       <c r="C47" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="D47" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C47,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$213:$D$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C47,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="E47" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C47,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$213:$E$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C47,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="F47" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C47,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$H$213:$H$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C47,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="G47" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C47,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$I$213:$I$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C47,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="H47" s="7">
-        <f>IF(F47="","",IF(F47=0,"n.a.",G47/F47))</f>
-        <v/>
+      <c r="D47" s="6" t="n">
+        <v>238122.69</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>809082.67</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>1047205.36</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>168170.21</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>0.1605895237205432</v>
       </c>
       <c r="I47" s="1" t="n"/>
       <c r="J47" s="1" t="n"/>
@@ -1692,25 +1605,20 @@
       <c r="C48" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D48" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C48,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$213:$D$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C48,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="E48" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C48,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$213:$E$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C48,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="F48" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C48,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$H$213:$H$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C48,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="G48" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C48,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$I$213:$I$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C48,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="H48" s="7">
-        <f>IF(F48="","",IF(F48=0,"n.a.",G48/F48))</f>
-        <v/>
+      <c r="D48" s="6" t="n">
+        <v>845719.74</v>
+      </c>
+      <c r="E48" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>845719.74</v>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>-423666.89</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>-0.5009542404674154</v>
       </c>
       <c r="I48" s="1" t="n"/>
       <c r="J48" s="1" t="n"/>
@@ -1726,26 +1634,11 @@
       <c r="C49" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D49" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C49,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$213:$D$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C49,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="E49" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C49,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$213:$E$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C49,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="F49" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C49,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$H$213:$H$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C49,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="G49" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C49,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$I$213:$I$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C49,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="H49" s="7">
-        <f>IF(F49="","",IF(F49=0,"n.a.",G49/F49))</f>
-        <v/>
-      </c>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="F49" s="6" t="n"/>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="7" t="n"/>
       <c r="I49" s="1" t="n"/>
       <c r="J49" s="1" t="n"/>
       <c r="K49" s="1" t="n"/>
@@ -1760,26 +1653,11 @@
       <c r="C50" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="D50" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C50,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$213:$D$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C50,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="E50" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C50,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$213:$E$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C50,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="F50" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C50,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$H$213:$H$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C50,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="G50" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C50,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$I$213:$I$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C50,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="H50" s="7">
-        <f>IF(F50="","",IF(F50=0,"n.a.",G50/F50))</f>
-        <v/>
-      </c>
+      <c r="D50" s="6" t="n"/>
+      <c r="E50" s="6" t="n"/>
+      <c r="F50" s="6" t="n"/>
+      <c r="G50" s="6" t="n"/>
+      <c r="H50" s="7" t="n"/>
       <c r="I50" s="1" t="n"/>
       <c r="J50" s="1" t="n"/>
       <c r="K50" s="1" t="n"/>
@@ -1794,26 +1672,11 @@
       <c r="C51" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="D51" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C51,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$D$213:$D$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C51,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="E51" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C51,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$E$213:$E$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C51,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="F51" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C51,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$H$213:$H$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C51,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="G51" s="6">
-        <f>IF(COUNTIFS('[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C51,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9)=0,"",SUMIFS('[D Finanzen.xlsx]D Finanzen'!$I$213:$I$263,'[D Finanzen.xlsx]D Finanzen'!$A$213:$A$263,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Finanzen.xlsx]D Finanzen'!$B$213:$B$263,C51,'[D Finanzen.xlsx]D Finanzen'!$C$213:$C$263,'[Steuerung.xlsx]Steuerung'!$F$9))</f>
-        <v/>
-      </c>
-      <c r="H51" s="7">
-        <f>IF(F51="","",IF(F51=0,"n.a.",G51/F51))</f>
-        <v/>
-      </c>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="F51" s="6" t="n"/>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="7" t="n"/>
       <c r="I51" s="1" t="n"/>
       <c r="J51" s="1" t="n"/>
       <c r="K51" s="1" t="n"/>
@@ -1975,6 +1838,8 @@
       <c r="N60" s="1" t="n"/>
       <c r="O60" s="1" t="n"/>
     </row>
+    <row r="61"/>
+    <row r="62"/>
     <row r="63">
       <c r="C63" t="inlineStr">
         <is>
